--- a/media/exports/reports/2026-01/growth-services.xlsx
+++ b/media/exports/reports/2026-01/growth-services.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>January's client work made $59,850 gross margin (64.8%). Consultant time not charged to client work took $8,330 and overheads $51,360, leaving $160 profit before tax (0.2% of revenue). To cover overheads, client work needs a 64.6% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>January's client work made $69,830 gross margin (68.2%). Consultant time not charged to client work took $15,180 and overheads $51,360, leaving $3,290 profit before tax (3.2% of revenue). To cover overheads, client work needs a 65.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -860,10 +860,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$92,370 against $88,250</t>
+          <t>$102,350 against $96,560</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$336,140 before overheads</t>
+          <t>$390,095 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is $524,320 this financial year to date (Jul to Jan 2026). Training makes the highest gross margin (75.7%); Projects the lowest (61.3%). The business needs 64.6% gross margin just to cover overheads.</t>
+          <t>Revenue is $578,275 this financial year to date (Jul to Jan 2026). Training makes the highest gross margin (77.9%); Projects the lowest (65.0%). The business needs 65.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Projects: 61.3% gross margin, 21.3 points over the 40.0% target ($69,112 ahead on $324,020 this financial year to date). Training: 75.7% gross margin, 35.7 points over the 40.0% target ($17,940 ahead on $50,200 this financial year to date).</t>
+          <t>Projects: 65.0% gross margin, 25.0 points over the 40.0% target ($89,665 ahead on $358,275 this financial year to date). Training: 77.9% gross margin, 37.9 points over the 40.0% target ($20,880 ahead on $55,100 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$60,170 against $66,850</t>
+          <t>$66,950 against $73,060</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$198,720 before overheads</t>
+          <t>$232,975 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Projects brought in $324,020 this financial year to date, at a 61.3% gross margin (below the 64.1% overall).</t>
+          <t>Projects brought in $358,275 this financial year to date, at a 65.0% gross margin (below the 67.5% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Projects: 61.3% gross margin, 21.3 points over the 40.0% target ($69,112 ahead on $324,020 this financial year to date).</t>
+          <t>Projects: 65.0% gross margin, 25.0 points over the 40.0% target ($89,665 ahead on $358,275 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$28,300 against $15,000</t>
+          <t>$31,100 against $16,500</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$99,400 before overheads</t>
+          <t>$114,200 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Retainers brought in $150,100 this financial year to date, at a 66.2% gross margin (above the 64.1% overall).</t>
+          <t>Retainers brought in $164,900 this financial year to date, at a 69.3% gross margin (above the 67.5% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 66.2% gross margin, 26.2 points over the 40.0% target ($39,360 ahead on $150,100 this financial year to date).</t>
+          <t>Retainers: 69.3% gross margin, 29.3 points over the 40.0% target ($48,240 ahead on $164,900 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$3,900 against $6,400</t>
+          <t>$4,300 against $7,000</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$38,020 before overheads</t>
+          <t>$42,920 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Training brought in $50,200 this financial year to date, at a 75.7% gross margin (above the 64.1% overall).</t>
+          <t>Training brought in $55,100 this financial year to date, at a 77.9% gross margin (above the 67.5% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Training: 75.7% gross margin, 35.7 points over the 40.0% target ($17,940 ahead on $50,200 this financial year to date).</t>
+          <t>Training: 77.9% gross margin, 37.9 points over the 40.0% target ($20,880 ahead on $55,100 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>59850</v>
+        <v>69830</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>38750</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>92370</v>
+        <v>102350</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the January 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the January 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>92370</v>
+        <v>102350</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>88250</v>
+        <v>96560</v>
       </c>
     </row>
     <row r="27">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>524320</v>
+        <v>578275</v>
       </c>
     </row>
     <row r="34">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>336140</v>
+        <v>390095</v>
       </c>
     </row>
     <row r="35">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>524320</v>
+        <v>578275</v>
       </c>
     </row>
     <row r="42">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>336140</v>
+        <v>390095</v>
       </c>
     </row>
     <row r="43">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>60170</v>
+        <v>66950</v>
       </c>
     </row>
     <row r="50">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>66850</v>
+        <v>73060</v>
       </c>
     </row>
     <row r="51">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>324020</v>
+        <v>358275</v>
       </c>
     </row>
     <row r="58">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>198720</v>
+        <v>232975</v>
       </c>
     </row>
     <row r="59">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>324020</v>
+        <v>358275</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>198720</v>
+        <v>232975</v>
       </c>
     </row>
     <row r="67">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
     </row>
     <row r="74">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="75">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>150100</v>
+        <v>164900</v>
       </c>
     </row>
     <row r="82">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>99400</v>
+        <v>114200</v>
       </c>
     </row>
     <row r="83">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>150100</v>
+        <v>164900</v>
       </c>
     </row>
     <row r="90">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>99400</v>
+        <v>114200</v>
       </c>
     </row>
     <row r="91">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="98">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="99">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="B105" s="12" t="n">
-        <v>50200</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="106">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="B106" s="12" t="n">
-        <v>38020</v>
+        <v>42920</v>
       </c>
     </row>
     <row r="107">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="B113" s="12" t="n">
-        <v>50200</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="114">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="B114" s="12" t="n">
-        <v>38020</v>
+        <v>42920</v>
       </c>
     </row>
     <row r="115">
@@ -2179,7 +2179,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2228,7 +2228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>94520</v>
+        <v>103550</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>35320</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>108140</v>
+        <v>118390</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>40040</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>114895</v>
+        <v>125715</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>42940</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>88250</v>
+        <v>96560</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>33260</v>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>111010</v>
+        <v>121275</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>42820</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>77175</v>
+        <v>84340</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>31940</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>63970</v>
+        <v>69985</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>25520</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>95555</v>
+        <v>104970</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>36100</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>90220</v>
+        <v>99060</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>35380</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>86320</v>
+        <v>94805</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>32820</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>61475</v>
+        <v>67745</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>21360</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>59535</v>
+        <v>65650</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>20280</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>71260</v>
+        <v>78550</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>25540</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>83940</v>
+        <v>92575</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>31140</v>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>69420</v>
+        <v>76600</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>24520</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>92370</v>
+        <v>102350</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>32520</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>70720</v>
+        <v>77350</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>27820</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>88540</v>
+        <v>96790</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>34400</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>94695</v>
+        <v>103515</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>36880</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>66850</v>
+        <v>73060</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>26240</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>84410</v>
+        <v>92075</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>34360</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>48975</v>
+        <v>53340</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>21860</v>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>37570</v>
+        <v>40885</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>17660</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>59755</v>
+        <v>65570</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>23980</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>64520</v>
+        <v>70760</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>26860</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>64820</v>
+        <v>71205</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>25920</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>38775</v>
+        <v>42845</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>13860</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>38035</v>
+        <v>42050</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>13560</v>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>45860</v>
+        <v>50650</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>18220</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>46840</v>
+        <v>51775</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>18960</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>29520</v>
+        <v>32800</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>12340</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>60170</v>
+        <v>66950</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>22440</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>4800</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>4800</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>5100</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>4920</v>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>5400</v>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>7980</v>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>7020</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>8460</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>7800</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>5940</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>5400</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>5760</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>5640</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>9480</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>9120</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>9360</v>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>2700</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>840</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>960</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>2100</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>3060</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>2100</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>840</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>14000</v>
+        <v>15400</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>3660</v>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>720</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>960</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>2100</v>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>960</v>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>9100</v>
+        <v>10000</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>1680</v>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>2700</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>3060</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>720</v>
@@ -4260,7 +4260,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4312,7 +4312,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>324020</v>
+        <v>358275</v>
       </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="13">
@@ -4364,7 +4364,7 @@
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>198720</v>
+        <v>232975</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>150100</v>
+        <v>164900</v>
       </c>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="13">
@@ -4386,7 +4386,7 @@
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>99400</v>
+        <v>114200</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>50200</v>
+        <v>55100</v>
       </c>
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="13">
@@ -4408,7 +4408,7 @@
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>38020</v>
+        <v>42920</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>524320</v>
+        <v>578275</v>
       </c>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="13">
@@ -4430,7 +4430,7 @@
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>336140</v>
+        <v>390095</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -4443,7 +4443,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-01/growth-services.xlsx
+++ b/media/exports/reports/2026-01/growth-services.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +149,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -818,7 +819,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -914,8 +915,8 @@
           <t>Year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B17" s="9">
-        <f>Workings!B35</f>
+      <c r="B17" s="11">
+        <f>Workings!B33</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1017,8 +1018,8 @@
           <t>Year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B29" s="9">
-        <f>Workings!B59</f>
+      <c r="B29" s="11">
+        <f>Workings!B57</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1120,8 +1121,8 @@
           <t>Year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B41" s="9">
-        <f>Workings!B83</f>
+      <c r="B41" s="11">
+        <f>Workings!B81</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1223,8 +1224,8 @@
           <t>Year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B53" s="9">
-        <f>Workings!B107</f>
+      <c r="B53" s="11">
+        <f>Workings!B105</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1288,7 +1289,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>Revenue, gross margin and growth by type of work, by month: every month is on the Data sheet.</t>
         </is>
@@ -1315,7 +1316,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1361,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1374,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
@@ -1393,7 +1394,7 @@
           <t>Gross margin on client work</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>69830</v>
       </c>
     </row>
@@ -1403,7 +1404,7 @@
           <t>Consultant wages and on-costs</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>45600</v>
       </c>
     </row>
@@ -1413,7 +1414,7 @@
           <t>Consultant time charged to client work (at cost)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>30420</v>
       </c>
     </row>
@@ -1423,7 +1424,7 @@
           <t>Consultant time not charged to client work</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -1434,7 +1435,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>B8-B11</f>
         <v/>
       </c>
@@ -1445,7 +1446,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>51360</v>
       </c>
     </row>
@@ -1455,7 +1456,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>B12-B13</f>
         <v/>
       </c>
@@ -1466,7 +1467,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>102350</v>
       </c>
     </row>
@@ -1476,7 +1477,7 @@
           <t>Gross margin on client work, %</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>B8/B15</f>
         <v/>
       </c>
@@ -1487,18 +1488,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Gross margin client work need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <f>(B11+B13)/B15</f>
         <v/>
       </c>
@@ -1520,7 +1521,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>January 2026 ÷ January 2025 − 1 (year on year)</t>
         </is>
@@ -1540,7 +1541,7 @@
           <t>Revenue, Jan 2026</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>102350</v>
       </c>
     </row>
@@ -1550,17 +1551,17 @@
           <t>Revenue, Jan 2025</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>96560</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="16">
         <f>B25/B26-1</f>
         <v/>
       </c>
@@ -1575,7 +1576,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1595,7 +1596,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>578275</v>
       </c>
     </row>
@@ -1605,17 +1606,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>390095</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <f>B34/B33</f>
         <v/>
       </c>
@@ -1630,7 +1631,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1650,7 +1651,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>578275</v>
       </c>
     </row>
@@ -1660,17 +1661,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="13" t="n">
         <v>390095</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="16">
         <f>B42/B41</f>
         <v/>
       </c>
@@ -1685,7 +1686,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>January 2026 ÷ January 2025 − 1 (year on year)</t>
         </is>
@@ -1705,7 +1706,7 @@
           <t>Revenue, Jan 2026</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="13" t="n">
         <v>66950</v>
       </c>
     </row>
@@ -1715,17 +1716,17 @@
           <t>Revenue, Jan 2025</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="13" t="n">
         <v>73060</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="16">
         <f>B49/B50-1</f>
         <v/>
       </c>
@@ -1740,7 +1741,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1760,7 +1761,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="13" t="n">
         <v>358275</v>
       </c>
     </row>
@@ -1770,17 +1771,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n">
+      <c r="B58" s="13" t="n">
         <v>232975</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="16">
         <f>B58/B57</f>
         <v/>
       </c>
@@ -1795,7 +1796,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1815,7 +1816,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>358275</v>
       </c>
     </row>
@@ -1825,17 +1826,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B66" s="12" t="n">
+      <c r="B66" s="13" t="n">
         <v>232975</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="16">
         <f>B66/B65</f>
         <v/>
       </c>
@@ -1850,7 +1851,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>January 2026 ÷ January 2025 − 1 (year on year)</t>
         </is>
@@ -1870,7 +1871,7 @@
           <t>Revenue, Jan 2026</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="13" t="n">
         <v>31100</v>
       </c>
     </row>
@@ -1880,17 +1881,17 @@
           <t>Revenue, Jan 2025</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n">
+      <c r="B74" s="13" t="n">
         <v>16500</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="B75" s="15">
+      <c r="B75" s="16">
         <f>B73/B74-1</f>
         <v/>
       </c>
@@ -1905,7 +1906,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1925,7 +1926,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="13" t="n">
         <v>164900</v>
       </c>
     </row>
@@ -1935,17 +1936,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B82" s="12" t="n">
+      <c r="B82" s="13" t="n">
         <v>114200</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="A83" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B83" s="15">
+      <c r="B83" s="16">
         <f>B82/B81</f>
         <v/>
       </c>
@@ -1960,7 +1961,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="inlineStr">
+      <c r="A87" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -1980,7 +1981,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B89" s="12" t="n">
+      <c r="B89" s="13" t="n">
         <v>164900</v>
       </c>
     </row>
@@ -1990,17 +1991,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B90" s="12" t="n">
+      <c r="B90" s="13" t="n">
         <v>114200</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="14" t="inlineStr">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B91" s="15">
+      <c r="B91" s="16">
         <f>B90/B89</f>
         <v/>
       </c>
@@ -2015,7 +2016,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>January 2026 ÷ January 2025 − 1 (year on year)</t>
         </is>
@@ -2035,7 +2036,7 @@
           <t>Revenue, Jan 2026</t>
         </is>
       </c>
-      <c r="B97" s="12" t="n">
+      <c r="B97" s="13" t="n">
         <v>4300</v>
       </c>
     </row>
@@ -2045,17 +2046,17 @@
           <t>Revenue, Jan 2025</t>
         </is>
       </c>
-      <c r="B98" s="12" t="n">
+      <c r="B98" s="13" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="15" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="B99" s="15">
+      <c r="B99" s="16">
         <f>B97/B98-1</f>
         <v/>
       </c>
@@ -2070,7 +2071,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="A103" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -2090,7 +2091,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B105" s="12" t="n">
+      <c r="B105" s="13" t="n">
         <v>55100</v>
       </c>
     </row>
@@ -2100,17 +2101,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B106" s="12" t="n">
+      <c r="B106" s="13" t="n">
         <v>42920</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="14" t="inlineStr">
+      <c r="A107" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B107" s="15">
+      <c r="B107" s="16">
         <f>B106/B105</f>
         <v/>
       </c>
@@ -2125,7 +2126,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="11" t="inlineStr">
+      <c r="A111" s="12" t="inlineStr">
         <is>
           <t>Financial year to date. Not available: the data starts October 2024.</t>
         </is>
@@ -2145,7 +2146,7 @@
           <t>Revenue, year to date (Jul to Jan 2026)</t>
         </is>
       </c>
-      <c r="B113" s="12" t="n">
+      <c r="B113" s="13" t="n">
         <v>55100</v>
       </c>
     </row>
@@ -2155,17 +2156,17 @@
           <t>Gross margin, year to date</t>
         </is>
       </c>
-      <c r="B114" s="12" t="n">
+      <c r="B114" s="13" t="n">
         <v>42920</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="inlineStr">
+      <c r="A115" s="15" t="inlineStr">
         <is>
           <t>Gross margin %, year to date</t>
         </is>
       </c>
-      <c r="B115" s="15">
+      <c r="B115" s="16">
         <f>B114/B113</f>
         <v/>
       </c>
@@ -2179,7 +2180,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2228,7 +2229,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2271,1985 +2272,1985 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
         <v>103550</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>35320</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IF(D6=0,"",F6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>118390</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>40040</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <f>IF(D7=0,"",F7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
         <v>125715</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <v>42940</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>IF(D8=0,"",F8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
         <v>96560</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>33260</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IF(D9=0,"",F9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
         <v>121275</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <v>42820</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>IF(D10=0,"",F10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
         <v>84340</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>31940</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>IF(D11=0,"",F11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>69985</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <v>25520</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IF(D12=0,"",F12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
         <v>104970</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>36100</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>IF(D13=0,"",F13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
         <v>99060</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <v>35380</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>IF(D14=0,"",F14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>94805</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <v>32820</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>IF(D15=0,"",F15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>67745</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <v>21360</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>IF(D16=0,"",F16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n">
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
         <v>65650</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="13" t="n">
         <v>20280</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>IF(D17=0,"",F17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
         <v>78550</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>25540</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="14">
         <f>IF(D18=0,"",F18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n">
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
         <v>92575</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="13" t="n">
         <v>31140</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <f>IF(D19=0,"",F19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n">
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="n">
         <v>76600</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>24520</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="14">
         <f>IF(D20=0,"",F20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n">
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
         <v>102350</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <v>32520</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <f>IF(D21=0,"",F21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>77350</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>27820</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="13">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="14">
         <f>IF(D22=0,"",F22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="n">
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
         <v>96790</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="13" t="n">
         <v>34400</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="13">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <f>IF(D23=0,"",F23/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n">
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
         <v>103515</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="13" t="n">
         <v>36880</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="13">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="14">
         <f>IF(D24=0,"",F24/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="n">
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
         <v>73060</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>26240</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="13">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <f>IF(D25=0,"",F25/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n">
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
         <v>92075</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>34360</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="13">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <f>IF(D26=0,"",F26/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n">
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
         <v>53340</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="13" t="n">
         <v>21860</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="13">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="14">
         <f>IF(D27=0,"",F27/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
         <v>40885</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <v>17660</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="13">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <f>IF(D28=0,"",F28/D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n">
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
         <v>65570</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="13" t="n">
         <v>23980</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="13">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="14">
         <f>IF(D29=0,"",F29/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n">
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
         <v>70760</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="13" t="n">
         <v>26860</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="13">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="14">
         <f>IF(D30=0,"",F30/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="n">
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>71205</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="13" t="n">
         <v>25920</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="13">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <f>IF(D31=0,"",F31/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="n">
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
         <v>42845</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="13" t="n">
         <v>13860</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="13">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="14">
         <f>IF(D32=0,"",F32/D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="n">
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="n">
         <v>42050</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="13" t="n">
         <v>13560</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="13">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="14">
         <f>IF(D33=0,"",F33/D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="n">
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
         <v>50650</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>18220</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="13">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="14">
         <f>IF(D34=0,"",F34/D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="n">
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
         <v>51775</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>18960</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="13">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="14">
         <f>IF(D35=0,"",F35/D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n">
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
         <v>32800</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="13" t="n">
         <v>12340</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="13">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="14">
         <f>IF(D36=0,"",F36/D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="n">
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
         <v>66950</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="13" t="n">
         <v>22440</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="13">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <f>IF(D37=0,"",F37/D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="n">
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
         <v>16500</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>4800</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="13">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <f>IF(D38=0,"",F38/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="n">
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
         <v>16500</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="13" t="n">
         <v>4800</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="13">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="14">
         <f>IF(D39=0,"",F39/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="n">
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
         <v>16500</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>5100</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="13">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="14">
         <f>IF(D40=0,"",F40/D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="n">
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
         <v>16500</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="13" t="n">
         <v>4920</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="13">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="14">
         <f>IF(D41=0,"",F41/D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
         <v>16500</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="13" t="n">
         <v>5400</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="13">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="14">
         <f>IF(D42=0,"",F42/D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="n">
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
         <v>24000</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="13" t="n">
         <v>7980</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="13">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="14">
         <f>IF(D43=0,"",F43/D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="n">
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
         <v>24000</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="13" t="n">
         <v>7020</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="13">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="13">
+      <c r="G44" s="14">
         <f>IF(D44=0,"",F44/D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="n">
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
         <v>24000</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="13" t="n">
         <v>8460</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="13">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="14">
         <f>IF(D45=0,"",F45/D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="n">
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
         <v>24000</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="13" t="n">
         <v>7800</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="13">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="13">
+      <c r="G46" s="14">
         <f>IF(D46=0,"",F46/D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="n">
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
         <v>17900</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="13" t="n">
         <v>5940</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="13">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="13">
+      <c r="G47" s="14">
         <f>IF(D47=0,"",F47/D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="n">
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
         <v>17900</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="13" t="n">
         <v>5400</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="13">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="13">
+      <c r="G48" s="14">
         <f>IF(D48=0,"",F48/D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
         <v>17900</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="13" t="n">
         <v>5760</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="13">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="14">
         <f>IF(D49=0,"",F49/D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="n">
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
         <v>17900</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="13" t="n">
         <v>5640</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="13">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="13">
+      <c r="G50" s="14">
         <f>IF(D50=0,"",F50/D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="n">
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
         <v>31100</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>9480</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="13">
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="14">
         <f>IF(D51=0,"",F51/D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="n">
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n">
         <v>31100</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="13" t="n">
         <v>9120</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="13">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="13">
+      <c r="G52" s="14">
         <f>IF(D52=0,"",F52/D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="n">
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
         <v>31100</v>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="13" t="n">
         <v>9360</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="13">
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="13">
+      <c r="G53" s="14">
         <f>IF(D53=0,"",F53/D53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="n">
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
         <v>9700</v>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="13" t="n">
         <v>2700</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="13">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="13">
+      <c r="G54" s="14">
         <f>IF(D54=0,"",F54/D54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="n">
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
         <v>5100</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="13" t="n">
         <v>840</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="13">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="14">
         <f>IF(D55=0,"",F55/D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="n">
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
         <v>5700</v>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="E56" s="13" t="n">
         <v>960</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="13">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="14">
         <f>IF(D56=0,"",F56/D56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="n">
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="n">
         <v>7000</v>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="E57" s="13" t="n">
         <v>2100</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="13">
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="14">
         <f>IF(D57=0,"",F57/D57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="n">
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
         <v>12700</v>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="E58" s="13" t="n">
         <v>3060</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="13">
         <f>D58-E58</f>
         <v/>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="14">
         <f>IF(D58=0,"",F58/D58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="n">
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
         <v>7000</v>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="E59" s="13" t="n">
         <v>2100</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="13">
         <f>D59-E59</f>
         <v/>
       </c>
-      <c r="G59" s="13">
+      <c r="G59" s="14">
         <f>IF(D59=0,"",F59/D59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="n">
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
         <v>5100</v>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="E60" s="13" t="n">
         <v>840</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="13">
         <f>D60-E60</f>
         <v/>
       </c>
-      <c r="G60" s="13">
+      <c r="G60" s="14">
         <f>IF(D60=0,"",F60/D60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="n">
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
         <v>15400</v>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="E61" s="13" t="n">
         <v>3660</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="13">
         <f>D61-E61</f>
         <v/>
       </c>
-      <c r="G61" s="13">
+      <c r="G61" s="14">
         <f>IF(D61=0,"",F61/D61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="n">
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
         <v>4300</v>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="E62" s="13" t="n">
         <v>720</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="13">
         <f>D62-E62</f>
         <v/>
       </c>
-      <c r="G62" s="13">
+      <c r="G62" s="14">
         <f>IF(D62=0,"",F62/D62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D63" s="12" t="n">
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
         <v>5700</v>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="E63" s="13" t="n">
         <v>960</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="13">
         <f>D63-E63</f>
         <v/>
       </c>
-      <c r="G63" s="13">
+      <c r="G63" s="14">
         <f>IF(D63=0,"",F63/D63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="n">
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n">
         <v>7000</v>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="E64" s="13" t="n">
         <v>2100</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="13">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="13">
+      <c r="G64" s="14">
         <f>IF(D64=0,"",F64/D64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="n">
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="n">
         <v>5700</v>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="E65" s="13" t="n">
         <v>960</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="13">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="13">
+      <c r="G65" s="14">
         <f>IF(D65=0,"",F65/D65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="n">
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="n">
         <v>10000</v>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="E66" s="13" t="n">
         <v>1680</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="13">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="13">
+      <c r="G66" s="14">
         <f>IF(D66=0,"",F66/D66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="n">
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="n">
         <v>9700</v>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="E67" s="13" t="n">
         <v>2700</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="13">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="13">
+      <c r="G67" s="14">
         <f>IF(D67=0,"",F67/D67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="n">
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="n">
         <v>12700</v>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="E68" s="13" t="n">
         <v>3060</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="13">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="13">
+      <c r="G68" s="14">
         <f>IF(D68=0,"",F68/D68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="n">
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="n">
         <v>4300</v>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E69" s="13" t="n">
         <v>720</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="13">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="13">
+      <c r="G69" s="14">
         <f>IF(D69=0,"",F69/D69)</f>
         <v/>
       </c>
@@ -4260,7 +4261,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4312,7 +4313,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: January 2026 · Data status: Dec 2025 locked · Jan 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -4350,89 +4351,89 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Projects</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>358275</v>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="13">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="14">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>232975</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>IF(B6=0,"",E6/B6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Retainers</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>164900</v>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="13">
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="14">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>114200</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>IF(B7=0,"",E7/B7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>55100</v>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="13">
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="14">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <v>42920</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>IF(B8=0,"",E8/B8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>578275</v>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="13">
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="14">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>390095</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>IF(B9=0,"",E9/B9)</f>
         <v/>
       </c>
@@ -4443,7 +4444,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
